--- a/healthcare_forms/011_beck_depression_inventory_questionnaire--healthcare_forms.xlsx
+++ b/healthcare_forms/011_beck_depression_inventory_questionnaire--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1279,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2395,17 +2395,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>loss_of_energy_choices</t>
+          <t>sleep_changes_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>i_do_not_have_enough_energy_to_do_anything</t>
+          <t>i_sleep_as_well_as_i_used_to</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>I do not have enough energy to do anything</t>
+          <t>I sleep as well as I used to</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>i_sleep_as_well_as_i_used_to</t>
+          <t>i_sleep_somewhat_more_than_usual</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>I sleep as well as I used to</t>
+          <t>I sleep somewhat more than usual</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>i_sleep_somewhat_more_than_usual</t>
+          <t>i_sleep_somewhat_less_than_usual</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>I sleep somewhat more than usual</t>
+          <t>I sleep somewhat less than usual</t>
         </is>
       </c>
     </row>
@@ -2451,29 +2451,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>i_sleep_somewhat_less_than_usual</t>
+          <t>i_sleep_a_lot_more_or_a_lot_less_than_usual</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>I sleep somewhat less than usual</t>
+          <t>I sleep a lot more or a lot less than usual</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sleep_changes_choices</t>
+          <t>irritability_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>i_sleep_a_lot_more_or_a_lot_less_than_usual</t>
+          <t>i_am_no_more_irritable_than_usual</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>I sleep a lot more or a lot less than usual</t>
+          <t>I am no more irritable than usual</t>
         </is>
       </c>
     </row>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>i_am_no_more_irritable_than_usual</t>
+          <t>i_am_more_irritable_than_usual</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>I am no more irritable than usual</t>
+          <t>I am more irritable than usual</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>i_am_more_irritable_than_usual</t>
+          <t>i_am_much_more_irritable_than_usual</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>I am more irritable than usual</t>
+          <t>I am much more irritable than usual</t>
         </is>
       </c>
     </row>
@@ -2519,29 +2519,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>i_am_much_more_irritable_than_usual</t>
+          <t>i_am_irritable_all_the_time</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>I am much more irritable than usual</t>
+          <t>I am irritable all the time</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>irritability_choices</t>
+          <t>appetite_changes_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>i_am_irritable_all_the_time</t>
+          <t>i_have_not_experienced_any_change_in_appetite</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>I am irritable all the time</t>
+          <t>I have not experienced any change in appetite</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>i_have_not_experienced_any_change_in_appetite</t>
+          <t>my_appetite_is_somewhat_less_than_usual</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>I have not experienced any change in appetite</t>
+          <t>My appetite is somewhat less than usual</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>my_appetite_is_somewhat_less_than_usual</t>
+          <t>my_appetite_is_much_less_than_before</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>My appetite is somewhat less than usual</t>
+          <t>My appetite is much less than before</t>
         </is>
       </c>
     </row>
@@ -2587,29 +2587,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>my_appetite_is_much_less_than_before</t>
+          <t>i_have_no_appetite_at_all</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>My appetite is much less than before</t>
+          <t>I have no appetite at all</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>appetite_changes_choices</t>
+          <t>concentration_difficulty_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>i_have_no_appetite_at_all</t>
+          <t>i_can_concentrate_as_well_as_ever</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>I have no appetite at all</t>
+          <t>I can concentrate as well as ever</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>i_can_concentrate_as_well_as_ever</t>
+          <t>i_cannot_concentrate_as_well_as_usual</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>I can concentrate as well as ever</t>
+          <t>I cannot concentrate as well as usual</t>
         </is>
       </c>
     </row>
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>i_cannot_concentrate_as_well_as_usual</t>
+          <t>it_is_hard_to_keep_my_mind_on_anything_for_very_long</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>I cannot concentrate as well as usual</t>
+          <t>It is hard to keep my mind on anything for very long</t>
         </is>
       </c>
     </row>
@@ -2655,29 +2655,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>it_is_hard_to_keep_my_mind_on_anything_for_very_long</t>
+          <t>i_find_i_cannot_concentrate_on_anything</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>It is hard to keep my mind on anything for very long</t>
+          <t>I find I cannot concentrate on anything</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>concentration_difficulty_choices</t>
+          <t>tiredness_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>i_find_i_cannot_concentrate_on_anything</t>
+          <t>i_am_no_more_tired_than_usual</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>I find I cannot concentrate on anything</t>
+          <t>I am no more tired than usual</t>
         </is>
       </c>
     </row>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>i_am_no_more_tired_than_usual</t>
+          <t>i_get_more_tired_than_usual</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>I am no more tired than usual</t>
+          <t>I get more tired than usual</t>
         </is>
       </c>
     </row>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>i_get_more_tired_than_usual</t>
+          <t>i_am_too_tired_to_do_a_lot_of_the_things_i_used_to_do</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>I get more tired than usual</t>
+          <t>I am too tired to do a lot of the things I used to do</t>
         </is>
       </c>
     </row>
@@ -2723,29 +2723,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>i_am_too_tired_to_do_a_lot_of_the_things_i_used_to_do</t>
+          <t>i_am_too_tired_to_do_most_of_the_things_i_used_to_do</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>I am too tired to do a lot of the things I used to do</t>
+          <t>I am too tired to do most of the things I used to do</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tiredness_choices</t>
+          <t>interest_in_sex_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>i_am_too_tired_to_do_most_of_the_things_i_used_to_do</t>
+          <t>i_have_not_noticed_any_recent_change_in_interest_in_sex</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>I am too tired to do most of the things I used to do</t>
+          <t>I have not noticed any recent change in interest in sex</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>i_have_not_noticed_any_recent_change_in_interest_in_sex</t>
+          <t>i_am_less_interested_in_sex_than_i_used_to_be</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>I have not noticed any recent change in interest in sex</t>
+          <t>I am less interested in sex than I used to be</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>i_am_less_interested_in_sex_than_i_used_to_be</t>
+          <t>i_have_almost_no_interest_in_sex</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>I am less interested in sex than I used to be</t>
+          <t>I have almost no interest in sex</t>
         </is>
       </c>
     </row>
@@ -2791,29 +2791,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>i_have_almost_no_interest_in_sex</t>
+          <t>i_have_lost_interest_in_sex_completely</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>I have almost no interest in sex</t>
+          <t>I have lost interest in sex completely</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>interest_in_sex_choices</t>
+          <t>follow_up_recommended_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>i_have_lost_interest_in_sex_completely</t>
+          <t>yes_urgent</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>I have lost interest in sex completely</t>
+          <t>Yes urgent</t>
         </is>
       </c>
     </row>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>yes_urgent</t>
+          <t>yes_routine</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Yes urgent</t>
+          <t>Yes routine</t>
         </is>
       </c>
     </row>
@@ -2842,27 +2842,10 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>yes_routine</t>
+          <t>no_follow-up_needed</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
-        <is>
-          <t>Yes routine</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>follow_up_recommended_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>no_follow-up_needed</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
         <is>
           <t>No follow-up needed</t>
         </is>
